--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,204 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126057952</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>585090</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7060066</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126059263</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58130</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585069</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7060189</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>126057952</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>126057952</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>126059263</v>
       </c>
       <c r="B17" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2419,108 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126270705</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100500</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Timmeråsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585006</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7060536</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>126057952</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>126059263</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126270705</v>
       </c>
       <c r="B18" t="n">
-        <v>100500</v>
+        <v>100504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>126270705</v>
       </c>
       <c r="B18" t="n">
-        <v>100504</v>
+        <v>100507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 40075-2024 artfynd.xlsx
+++ b/artfynd/A 40075-2024 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>126057952</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>126059263</v>
       </c>
       <c r="B17" t="n">
-        <v>58135</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126270705</v>
       </c>
       <c r="B18" t="n">
-        <v>100507</v>
+        <v>100516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
